--- a/legacy/Documentation/Internship purchased items.xlsx
+++ b/legacy/Documentation/Internship purchased items.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joshbond/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LabPulse Tommy\LabPulse\legacy\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA08BC03-6160-6F43-B12D-BC5C827F8BAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{888F2845-F990-4C66-B9E0-2AE4915D7005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="5040" windowWidth="25500" windowHeight="13260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,12 +31,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Item quantity</t>
   </si>
@@ -117,6 +120,9 @@
   </si>
   <si>
     <t>USB Hub 4 ports</t>
+  </si>
+  <si>
+    <t>NOTE: The UPS hat was an old model used in a prototype. We have since swapped to https://thepihut.com/products/suptronics-x1200-5-1v-5a-ups-for-raspberry-pi-5</t>
   </si>
 </sst>
 </file>
@@ -124,7 +130,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="44" formatCode="_(&quot;£&quot;* #,##0.00_);_(&quot;£&quot;* \(#,##0.00\);_(&quot;£&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(&quot;£&quot;* #,##0.00_);_(&quot;£&quot;* \(#,##0.00\);_(&quot;£&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -186,9 +192,9 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -196,7 +202,7 @@
   </cellStyles>
   <dxfs count="1">
     <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;£&quot;* #,##0.00_);_(&quot;£&quot;* \(#,##0.00\);_(&quot;£&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="164" formatCode="_(&quot;£&quot;* #,##0.00_);_(&quot;£&quot;* \(#,##0.00\);_(&quot;£&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -545,15 +551,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -567,7 +573,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -582,7 +588,7 @@
         <v>529.7116666666667</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -593,7 +599,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -604,7 +610,7 @@
         <v>22.27</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -615,7 +621,7 @@
         <v>7.17</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -626,7 +632,7 @@
         <v>7.38</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -637,7 +643,7 @@
         <v>1.58</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
@@ -648,7 +654,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -659,7 +665,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
@@ -670,7 +676,7 @@
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
@@ -681,7 +687,7 @@
         <v>63.92</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
@@ -691,8 +697,11 @@
       <c r="C12" s="2">
         <v>19.75</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
@@ -704,7 +713,7 @@
         <v>3.75</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>16</v>
       </c>
@@ -715,7 +724,7 @@
         <v>1.74</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>17</v>
       </c>
@@ -726,7 +735,7 @@
         <v>2.5299999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>18</v>
       </c>
@@ -737,7 +746,7 @@
         <v>1.79</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>19</v>
       </c>
@@ -749,7 +758,7 @@
         <v>6.6583333333333341</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>20</v>
       </c>
@@ -760,7 +769,7 @@
         <v>0.48</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>21</v>
       </c>
@@ -771,7 +780,7 @@
         <v>4.99</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>22</v>
       </c>
@@ -782,7 +791,7 @@
         <v>5.22</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>23</v>
       </c>
@@ -794,7 +803,7 @@
         <v>3.4083333333333332</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>24</v>
       </c>
@@ -805,7 +814,7 @@
         <v>3.88</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>25</v>
       </c>
@@ -816,7 +825,7 @@
         <v>6.53</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>26</v>
       </c>
@@ -827,13 +836,13 @@
         <v>5.25</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C27" s="2"/>
     </row>
   </sheetData>
